--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111788606</v>
+        <v>111788414</v>
       </c>
       <c r="B4" t="n">
-        <v>88899</v>
+        <v>89043</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,30 +947,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -978,14 +978,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>John Bauerskogen/Strömsbergs bruk, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642102</v>
+        <v>642126</v>
       </c>
       <c r="R4" t="n">
-        <v>6698252</v>
+        <v>6698336</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111788414</v>
+        <v>111931635</v>
       </c>
       <c r="B5" t="n">
-        <v>89043</v>
+        <v>90806</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,48 +1057,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>720</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>John Bauerskogen/Strömsbergs bruk, Upl</t>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642126</v>
+        <v>642302</v>
       </c>
       <c r="R5" t="n">
-        <v>6698336</v>
+        <v>6698305</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,12 +1118,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1135,16 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1155,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111931635</v>
+        <v>111979876</v>
       </c>
       <c r="B6" t="n">
-        <v>90806</v>
+        <v>90814</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,44 +1173,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
+          <t>Strömsbergs bruk , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>642302</v>
+        <v>642175</v>
       </c>
       <c r="R6" t="n">
-        <v>6698305</v>
+        <v>6698319</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,12 +1238,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,16 +1265,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1271,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111979876</v>
+        <v>111979480</v>
       </c>
       <c r="B7" t="n">
-        <v>90814</v>
+        <v>89057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1293,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>720</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strömsbergs bruk , Upl</t>
@@ -1353,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,9 +1380,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1391,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111979480</v>
+        <v>111980195</v>
       </c>
       <c r="B8" t="n">
-        <v>89057</v>
+        <v>90832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,43 +1415,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>720</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk , Upl</t>
+          <t>Tierp, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>642175</v>
+        <v>642102</v>
       </c>
       <c r="R8" t="n">
-        <v>6698319</v>
+        <v>6698252</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1471,7 +1479,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,11 +1500,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1513,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111980195</v>
+        <v>112030310</v>
       </c>
       <c r="B9" t="n">
-        <v>90832</v>
+        <v>56446</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,38 +1532,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>642102</v>
+        <v>642302</v>
       </c>
       <c r="R9" t="n">
-        <v>6698252</v>
+        <v>6698305</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,22 +1591,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,123 +1630,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112030310</v>
-      </c>
-      <c r="B10" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>642302</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6698305</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Tolfta</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Lotta Lund</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Lotta Lund</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,628 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128344573</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90818</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Tolfta, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>642149</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6698278</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128344407</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90832</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>720</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>642124</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6698335</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128344393</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90832</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>720</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>642186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6698296</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128344431</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90818</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>642119</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6698241</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128344230</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92663</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>642117</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6698299</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128344358</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bauerskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>642101</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6698271</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lotta Lund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90818</v>
+        <v>90835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R10" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90832</v>
+        <v>90821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R11" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90832</v>
+        <v>90835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90818</v>
+        <v>90821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B10" t="n">
-        <v>90835</v>
+        <v>90913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R10" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B11" t="n">
-        <v>90821</v>
+        <v>90927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R11" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90835</v>
+        <v>90927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90821</v>
+        <v>90913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90913</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R10" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90927</v>
+        <v>90913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R11" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
         <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>90939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90913</v>
+        <v>90925</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90927</v>
+        <v>90939</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90913</v>
+        <v>90925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
         <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
         <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B10" t="n">
-        <v>90942</v>
+        <v>90955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R10" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B11" t="n">
-        <v>90928</v>
+        <v>90969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R11" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B10" t="n">
-        <v>90955</v>
+        <v>90979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R10" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B11" t="n">
-        <v>90969</v>
+        <v>90965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R11" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90969</v>
+        <v>90979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>90965</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92802</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344407</v>
+        <v>128344573</v>
       </c>
       <c r="B10" t="n">
-        <v>90979</v>
+        <v>90965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642124</v>
+        <v>642149</v>
       </c>
       <c r="R10" t="n">
-        <v>6698335</v>
+        <v>6698278</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,32 +1734,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344573</v>
+        <v>128344407</v>
       </c>
       <c r="B11" t="n">
-        <v>90965</v>
+        <v>90979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,17 +1768,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642149</v>
+        <v>642124</v>
       </c>
       <c r="R11" t="n">
-        <v>6698278</v>
+        <v>6698335</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
         <v>128344573</v>
       </c>
       <c r="B10" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>128344407</v>
       </c>
       <c r="B11" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>128344393</v>
       </c>
       <c r="B12" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>128344431</v>
       </c>
       <c r="B13" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>128344358</v>
       </c>
       <c r="B15" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96862551</v>
+        <v>111788414</v>
       </c>
       <c r="B2" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -718,14 +713,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk , Upl</t>
+          <t>John Bauerskogen/Strömsbergs bruk, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642175.212860164</v>
+        <v>642126</v>
       </c>
       <c r="R2" t="n">
-        <v>6698319.320043332</v>
+        <v>6698336</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,16 +764,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -805,57 +780,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96862643</v>
+        <v>111979480</v>
       </c>
       <c r="B3" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>Strömsbergs bruk , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642102.0428085228</v>
+        <v>642175</v>
       </c>
       <c r="R3" t="n">
-        <v>6698251.641631705</v>
+        <v>6698320</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,22 +850,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,18 +874,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,19 +897,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111788414</v>
+        <v>128344393</v>
       </c>
       <c r="B4" t="n">
-        <v>89043</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -970,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -978,17 +935,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>John Bauerskogen/Strömsbergs bruk, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>642126</v>
+        <v>642186</v>
       </c>
       <c r="R4" t="n">
-        <v>6698336</v>
+        <v>6698296</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,37 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111931635</v>
+        <v>128344407</v>
       </c>
       <c r="B5" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,17 +1036,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>642302</v>
+        <v>642124</v>
       </c>
       <c r="R5" t="n">
-        <v>6698305</v>
+        <v>6698335</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,16 +1087,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1161,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111979876</v>
+        <v>96862551</v>
       </c>
       <c r="B6" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,7 +1148,7 @@
         <v>642175</v>
       </c>
       <c r="R6" t="n">
-        <v>6698319</v>
+        <v>6698320</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,22 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,6 +1192,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1281,55 +1218,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111979480</v>
+        <v>96862643</v>
       </c>
       <c r="B7" t="n">
-        <v>89057</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>720</v>
+        <v>3286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk , Upl</t>
+          <t>Tierp, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>642175</v>
+        <v>642103</v>
       </c>
       <c r="R7" t="n">
-        <v>6698319</v>
+        <v>6698251</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:47</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,12 +1304,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1403,15 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111980195</v>
+        <v>128344431</v>
       </c>
       <c r="B8" t="n">
-        <v>90832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,38 +1344,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>Bauerskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>642102</v>
+        <v>642119</v>
       </c>
       <c r="R8" t="n">
-        <v>6698252</v>
+        <v>6698241</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,22 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,6 +1419,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1516,15 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112030310</v>
+        <v>128344573</v>
       </c>
       <c r="B9" t="n">
-        <v>56446</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,42 +1449,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>3286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strömsbergs bruk/spökskogen, Upl</t>
+          <t>Bauerskogen, Tolfta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>642302</v>
+        <v>642149</v>
       </c>
       <c r="R9" t="n">
-        <v>6698305</v>
+        <v>6698278</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,22 +1506,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,6 +1520,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1633,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128344573</v>
+        <v>111931635</v>
       </c>
       <c r="B10" t="n">
-        <v>90969</v>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,17 +1573,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bauerskogen, Tolfta, Upl</t>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>642149</v>
+        <v>642301</v>
       </c>
       <c r="R10" t="n">
-        <v>6698278</v>
+        <v>6698305</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,12 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,6 +1624,16 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1734,35 +1650,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344407</v>
+        <v>128344358</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1772,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>642124</v>
+        <v>642101</v>
       </c>
       <c r="R11" t="n">
-        <v>6698335</v>
+        <v>6698271</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128344393</v>
+        <v>111979876</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>720</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1873,17 +1793,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Strömsbergs bruk , Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>642186</v>
+        <v>642175</v>
       </c>
       <c r="R12" t="n">
-        <v>6698296</v>
+        <v>6698320</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1907,12 +1827,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128344431</v>
+        <v>111980195</v>
       </c>
       <c r="B13" t="n">
-        <v>90969</v>
+        <v>93215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,44 +1881,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Tierp, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>642119</v>
+        <v>642103</v>
       </c>
       <c r="R13" t="n">
-        <v>6698241</v>
+        <v>6698251</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,12 +1936,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +1960,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2048,7 +1981,7 @@
         <v>128344230</v>
       </c>
       <c r="B14" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2150,55 +2083,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128344358</v>
+        <v>112030310</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bauerskogen, Upl</t>
+          <t>Strömsbergs bruk/spökskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>642101</v>
+        <v>642301</v>
       </c>
       <c r="R15" t="n">
-        <v>6698271</v>
+        <v>6698305</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2222,12 +2153,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,7 +2177,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8507-2023 artfynd.xlsx
+++ b/artfynd/A 8507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111788414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111979480</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96862551</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96862643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344573</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111931635</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344358</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111979876</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111980195</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344230</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,8 +2262,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112030310</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>